--- a/output/19609153_Korea_Republic_vs_Czech_Republic/tactical_analysis.xlsx
+++ b/output/19609153_Korea_Republic_vs_Czech_Republic/tactical_analysis.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.21</v>
+        <v>0.211</v>
       </c>
       <c r="E2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="3">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="E4" t="n">
         <v>1.33</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.179</v>
+        <v>0.182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.273</v>
+        <v>0.275</v>
       </c>
       <c r="E5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="6">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.9</v>
+        <v>17.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>0.017</v>
       </c>
       <c r="E8" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="9">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E2" t="n">
-        <v>3.118</v>
+        <v>3.36</v>
       </c>
       <c r="F2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="E3" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>2.09</v>
       </c>
       <c r="E4" t="n">
-        <v>216.667</v>
+        <v>225</v>
       </c>
       <c r="F4" t="n">
         <v>1.39</v>
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="E6" t="n">
-        <v>1.186</v>
+        <v>1.1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="E9" t="n">
         <v>2.143</v>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.127</v>
+        <v>0.149</v>
       </c>
       <c r="F10" t="n">
         <v>0.8</v>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="E11" t="n">
-        <v>3.395</v>
+        <v>2.752</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E13" t="n">
-        <v>2.754</v>
+        <v>3.188</v>
       </c>
       <c r="F13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="E14" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>2.09</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>106.667</v>
       </c>
       <c r="F15" t="n">
         <v>1.39</v>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="E17" t="n">
-        <v>1.121</v>
+        <v>0.959</v>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="E19" t="n">
         <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="E20" t="n">
         <v>0.778</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.112</v>
+        <v>0.121</v>
       </c>
       <c r="F21" t="n">
         <v>0.8</v>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>1.294</v>
+        <v>1.109</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.47</v>
+        <v>-0.45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="8">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="9"/>
@@ -1696,7 +1696,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>韩国队以62%的控球率和541次传球编织了一张覆盖全场的控制网，长传仅占传球的11.1%，球权推进耐心而细腻。捷克则交出截然不同的答案——传球总数仅324次，但长传比例高达21.0%，向前传球的倾向比韩国高出近十个百分点。这不是一场对等的传控对决，而是一方用层层递进的短传梳理比赛，另一方则以直接、垂直的方式寻找突破缝隙。</t>
+          <t>韩国队将比赛纳入了自己熟悉的节奏。六成以上的控球率与541次传球，勾勒出一支试图通过传控来拆解对手的球队。他们的长传只占传球总数的11%，传中更是低至2%，这并非一支盲目向禁区起球的队伍。捷克则选择了截然不同的推进方式——长传占比达到21%，向前传球比例高达27%，每一次得球都透着直接冲击对方防线的意图。控球率不足四成，总传球数也仅有327次，捷克人并不追求球权，他们要的是效率。</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>控球率在六个时间窗口内纹丝不动——62%对38%，韩国队从开场到终场哨响始终握着方向盘。但这组稳定数字之下，比赛的呼吸节奏却在不断变换。前十五分钟韩国的压迫强度达到12.0，五次射门累积0.496的期望进球，而捷克颗粒无收。捷克真正的锐利出现在第59分钟进球之后：尽管控球率未变，他们在最后十五分钟突然释放出五次射门、0.558的期望进球，且射正后的期望进球高达1.241，每一次打正都极具威胁。韩国的射门质量同样出色——全场期望进球1.69，射正后跃升至2.28，说明一旦命中门框范围，就几乎不给门将留下反应余地。</t>
+          <t>比赛开局，捷克反客为主。0-15分钟他们拿到57%控球率，逼得韩国队一度失去节奏。但韩国在15-30分钟窗口迅速调整，控球率反超至57%，此后再未让对手在场面控制上占得便宜——45分钟后稳步攀升，直到比赛末段达到63.4%的峰值。压迫强度数据揭示了背后的原因：韩国全场压迫强度仅13.1，远低于捷克的17.5，这意味着韩国人逼抢更凶狠、更靠前。第59分钟捷克进球是一个拐点。进球后捷克控球率反而从42.6%跌至38%，韩国则在丢球后掌控力增强，射门xG维持在0.364。第67分钟黄仁范扳平后，韩国控球优势进一步拉大，捷克反扑的窗口仅在第80分钟吴贤揆破门后短暂打开——他们最后10分钟轰出5脚射门，累计xG达0.652，但为时已晚。全场韩国xGOT达到2.40，明显高于xG的1.82，说明他们的射门质量极佳，每次打正都让门将难以应对。</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>韩国在进攻端做到了几乎所有他们想做的事：传控渗透、长传冲击、传中抢点、三区穿插和向前推进，五条线路全部打通。防守端的高位抢断和压迫限制效果显著，封堵和解围倾向高达0.600，显示出他们在丢掉球权后立即收紧空间的决心。捷克在进攻端同样亮点不少——传控、传中、三区穿插和向前推进都收到了实效，但长传冲击的效率偏低，未能真正撼动韩国的防线。防守层面，捷克的压迫限制和高位抢断存在明显缺口，线路拦截也未能有效切断韩国的传球网络。</t>
+          <t>韩国在进攻端展现了手段的多样性。传控渗透、长传冲击、传中抢点、三区穿插与向前推进，五条通路全部走通。防守端同样扎实——高位抢断比例高出对手，压迫强度更优，落位后的封堵与解围倾向达到0.6，说明他们并不忌讳用最直接的方式清除危险。反观捷克，进攻虽有传控渗透和传中抢点的亮点，但长传冲击这条路径效率偏低，未能有效撕开韩国防线。防守端问题更明显：压迫限制不足、高位抢断寥寥、线路拦截也未能奏效，唯一值得称道的只有落位防守这一环。德国人踢得勇敢，但漏洞比对手多。</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>这场比赛在战术层面的核心碰撞，是捷克的三区穿插与韩国落位防守之间的反复试探。捷克在进攻三区传球占比达到15.7%，高于韩国的11.8%，他们确实找到了插进韩国防守腹地的路径——第59分钟的进球正是这种穿透力的直接证明。但韩国以全场12.0的压迫强度牢牢钳制着捷克的出球源头，高位抢断比例0.022对0.017的优势看似微小，却让捷克在由守转攻的瞬间屡屡被截断节奏。韩国打的是克制，捷克打的是冲击，前者在这场博弈中多了一分从容。</t>
+          <t>这是一场转换大战，双方都试图用快速推进惩罚对方。捷克在“三区穿插”这一环上确实找到了韩国的缝隙——他们的进攻三区传球占比达到15.9%，高于对手的12%，说明在对方腹地的衔接做得很聪明，一度撕开了韩国的落位防守。但韩国的应对更加完整。他们用凶狠的高位压迫掐断了捷克由守转攻的第一脚出球——压迫强度13.1对17.5的优势，让捷克的长传快攻无从发起。球权丢失后的反抢效率，成了这场比赛的隐形分水岭。韩国的控球率优势不是漫无目的的倒脚，而是持续向捷克施压、迫使他们犯错的手段。</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>韩国用无孔不入的控球和高质量的终结覆盖了一场本可陷入泥潭的比赛，捷克在有限的反抗中打出了效率，却无法撼动控制权的根本格局。</t>
+          <t>韩国用持续的控球压迫将对手拖入消耗战，捷克的反击锐利但无法持久。</t>
         </is>
       </c>
     </row>
